--- a/006 TKI - CLIENT Best Negotiating Practices - DATE.xlsx
+++ b/006 TKI - CLIENT Best Negotiating Practices - DATE.xlsx
@@ -1,26 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\OneDrive\Documents\Watershed\Tasklist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E0A596F-E5C1-43CD-AB38-18DBDD1624E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AECEE27-BDF1-4027-BF8C-3D3AE7533063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pre-work" sheetId="1" r:id="rId1"/>
     <sheet name="TKI Chart" sheetId="2" r:id="rId2"/>
     <sheet name="Pre-work - Attendees only" sheetId="3" r:id="rId3"/>
-    <sheet name="TKI Chart- Attendees only" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TKI Chart'!$A$4:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TKI Chart- Attendees only'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,8 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -46,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t>Client</t>
   </si>
@@ -146,69 +142,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>ALICIA DELGADO</t>
-  </si>
-  <si>
-    <t>ALISHA CARROLL</t>
-  </si>
-  <si>
-    <t>BILLY BLEM</t>
-  </si>
-  <si>
-    <t>BRANDON BLACK</t>
-  </si>
-  <si>
-    <t>BRIAN SMITH</t>
-  </si>
-  <si>
-    <t>BROCK ALLEN</t>
-  </si>
-  <si>
-    <t>COLE WATSON</t>
-  </si>
-  <si>
-    <t>EMILY FRIEDLANDER</t>
-  </si>
-  <si>
-    <t>JOSHUA DIXON</t>
-  </si>
-  <si>
-    <t>Kashif Javed</t>
-  </si>
-  <si>
-    <t>KATHRYN BLANCHETTE</t>
-  </si>
-  <si>
-    <t>Kristina Hayek</t>
-  </si>
-  <si>
-    <t>MATT BERTHELOT</t>
-  </si>
-  <si>
-    <t>MATT STOCKDALE</t>
-  </si>
-  <si>
-    <t>MATTHEW YOUNGER</t>
-  </si>
-  <si>
-    <t>MEREDITH BERRY</t>
-  </si>
-  <si>
-    <t>Ryan Boyle</t>
-  </si>
-  <si>
-    <t>STEPHEN CHEN</t>
-  </si>
-  <si>
-    <t>STEPHEN GRAY</t>
-  </si>
-  <si>
-    <t>THOMAS ENSLEY</t>
-  </si>
-  <si>
-    <t>TYLER SANEHOLTZ</t>
-  </si>
-  <si>
     <t>Watershed Associates - Online TKI Results Chart</t>
   </si>
   <si>
@@ -219,6 +152,12 @@
   </si>
   <si>
     <t>Least used</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -</t>
   </si>
 </sst>
 </file>
@@ -393,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -446,17 +385,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -934,19 +867,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Accommodating</c:v>
+                  <c:v>Most</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Competing</c:v>
+                  <c:v>Least</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Collaborating</c:v>
+                  <c:v> -</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Compromising</c:v>
+                  <c:v> -</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Avoiding</c:v>
+                  <c:v> -</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -958,19 +891,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1007,19 +940,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Accommodating</c:v>
+                  <c:v>Most</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Competing</c:v>
+                  <c:v>Least</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Collaborating</c:v>
+                  <c:v> -</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Compromising</c:v>
+                  <c:v> -</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Avoiding</c:v>
+                  <c:v> -</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1031,19 +964,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1051,274 +984,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-0915-4FD7-83D5-ECF3009AF713}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="1758580928"/>
-        <c:axId val="1758583248"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1758580928"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1758583248"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1758583248"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1758580928"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="1" l="0.75" r="0.75" t="1" header="0.5" footer="0.5"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="118"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="18"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.7423109443534301E-2"/>
-          <c:y val="1.8126888217522698E-2"/>
-          <c:w val="0.82514374042170902"/>
-          <c:h val="0.9526017888540631"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'TKI Chart- Attendees only'!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Most used</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'TKI Chart- Attendees only'!$A$4:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Accommodating</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Competing</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Collaborating</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Compromising</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Avoiding</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'TKI Chart- Attendees only'!$B$4:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C9C5-485B-B825-19C6383CED30}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'TKI Chart- Attendees only'!$C$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Least used</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="92D050"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'TKI Chart- Attendees only'!$A$4:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Accommodating</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Competing</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Collaborating</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Compromising</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Avoiding</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'TKI Chart- Attendees only'!$C$4:$C$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C9C5-485B-B825-19C6383CED30}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1439,49 +1104,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F24EB48A-0E41-4EB4-B07D-441BD34295DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1837,15 +1459,13 @@
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
       <c r="Q1" s="10"/>
@@ -1918,7 +1538,7 @@
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
     </row>
-    <row r="5" spans="1:18" ht="76.5" thickBot="1">
+    <row r="5" spans="1:18" ht="95.25" thickBot="1">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
@@ -1965,18 +1585,18 @@
         <v>1</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="12"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
       <c r="G6" s="19" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="19" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="18"/>
@@ -1990,19 +1610,19 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="22" t="s">
-        <v>10</v>
+      <c r="B7" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -2017,18 +1637,18 @@
         <v>3</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="12"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="19" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="18"/>
@@ -2042,19 +1662,19 @@
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>30</v>
+      <c r="B9" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="12"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
-      <c r="G9" s="20" t="s">
-        <v>12</v>
+      <c r="G9" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="20" t="s">
-        <v>11</v>
+      <c r="I9" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -2068,19 +1688,19 @@
       <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="19" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="12"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
-        <v>12</v>
+      <c r="G10" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H10" s="17"/>
-      <c r="I10" s="18" t="s">
-        <v>14</v>
+      <c r="I10" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="18"/>
@@ -2094,19 +1714,19 @@
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>32</v>
+      <c r="B11" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="12"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
-      <c r="G11" s="20" t="s">
-        <v>10</v>
+      <c r="G11" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="20" t="s">
-        <v>12</v>
+      <c r="I11" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -2121,20 +1741,18 @@
         <v>7</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="12"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
       <c r="G12" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>11</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H12" s="17"/>
       <c r="I12" s="19" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="18"/>
@@ -2148,19 +1766,19 @@
       <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>34</v>
+      <c r="B13" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="12"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
-      <c r="G13" s="20" t="s">
-        <v>11</v>
+      <c r="G13" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="20" t="s">
-        <v>12</v>
+      <c r="I13" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
@@ -2174,19 +1792,19 @@
       <c r="A14" s="9">
         <v>9</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>35</v>
+      <c r="B14" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="12"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="18" t="s">
-        <v>13</v>
+      <c r="G14" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H14" s="17"/>
-      <c r="I14" s="18" t="s">
-        <v>12</v>
+      <c r="I14" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="18"/>
@@ -2200,19 +1818,19 @@
       <c r="A15" s="9">
         <v>10</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>36</v>
+      <c r="B15" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="12"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
-      <c r="G15" s="20" t="s">
-        <v>13</v>
+      <c r="G15" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H15" s="17"/>
-      <c r="I15" s="20" t="s">
-        <v>11</v>
+      <c r="I15" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -2227,18 +1845,18 @@
         <v>11</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="12"/>
       <c r="E16" s="17"/>
       <c r="F16" s="18"/>
       <c r="G16" s="19" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="19" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="18"/>
@@ -2252,19 +1870,19 @@
       <c r="A17" s="9">
         <v>12</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>38</v>
+      <c r="B17" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="12"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
-      <c r="G17" s="20" t="s">
-        <v>10</v>
+      <c r="G17" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H17" s="17"/>
-      <c r="I17" s="20" t="s">
-        <v>13</v>
+      <c r="I17" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -2279,18 +1897,18 @@
         <v>13</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="12"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="19" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="19" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="18"/>
@@ -2304,19 +1922,19 @@
       <c r="A19" s="9">
         <v>14</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>40</v>
+      <c r="B19" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="12"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="20" t="s">
-        <v>10</v>
+      <c r="G19" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H19" s="17"/>
-      <c r="I19" s="20" t="s">
-        <v>13</v>
+      <c r="I19" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
@@ -2331,18 +1949,18 @@
         <v>15</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="12"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="19" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="18"/>
@@ -2356,19 +1974,19 @@
       <c r="A21" s="9">
         <v>16</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="22" t="s">
-        <v>11</v>
+      <c r="B21" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -2383,18 +2001,18 @@
         <v>17</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="12"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="19" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="18"/>
@@ -2408,19 +2026,19 @@
       <c r="A23" s="16">
         <v>18</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>44</v>
+      <c r="B23" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="12"/>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="20" t="s">
-        <v>11</v>
+      <c r="G23" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H23" s="17"/>
-      <c r="I23" s="20" t="s">
-        <v>13</v>
+      <c r="I23" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -2434,23 +2052,23 @@
       <c r="A24" s="9">
         <v>19</v>
       </c>
-      <c r="B24" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="23"/>
-      <c r="I24" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="23"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
+      <c r="B24" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="22"/>
+      <c r="I24" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
@@ -2460,19 +2078,19 @@
       <c r="A25" s="9">
         <v>20</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>46</v>
+      <c r="B25" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="12"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
-      <c r="G25" s="20" t="s">
-        <v>14</v>
+      <c r="G25" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="H25" s="17"/>
-      <c r="I25" s="20" t="s">
-        <v>11</v>
+      <c r="I25" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
@@ -2487,18 +2105,18 @@
         <v>21</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="12"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="19" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="18"/>
@@ -2552,7 +2170,7 @@
     <mergeCell ref="C1:I1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22:G27 H6:H27 J6:J27 I22:I27" xr:uid="{E120FCA4-4992-A647-AA3A-8E939067BF05}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G27 H6:H27 J6:J27 I27" xr:uid="{E120FCA4-4992-A647-AA3A-8E939067BF05}">
       <formula1>"Accommodating, Avoiding, Competing, Compromising, Collaborating"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2580,86 +2198,86 @@
   <sheetData>
     <row r="1" spans="1:3" ht="33.75">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4">
         <f>COUNTIF(Table6[[Most]:[2nd Most (If Tied or to offset tied Least)]],"Accommodating")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4">
         <f>COUNTIF(Table6[[Least]:[2nd Least (is tied or to offset the tied mosts)]],"Accommodating")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(Table6[[Most]:[2nd Most (If Tied or to offset tied Least)]],"Competing")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C5" s="4">
         <f>COUNTIF(Table6[[Least]:[2nd Least (is tied or to offset the tied mosts)]],"Competing")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B6" s="6">
         <f>COUNTIF(Table6[[Most]:[2nd Most (If Tied or to offset tied Least)]],"Collaborating")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6" s="6">
         <f>COUNTIF(Table6[[Least]:[2nd Least (is tied or to offset the tied mosts)]],"Collaborating")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4">
         <f>COUNTIF(Table6[[Most]:[2nd Most (If Tied or to offset tied Least)]],"Compromising")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4">
         <f>COUNTIF(Table6[[Least]:[2nd Least (is tied or to offset the tied mosts)]],"Compromising")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B8" s="6">
         <f>COUNTIF(Table6[[Most]:[2nd Most (If Tied or to offset tied Least)]],"Avoiding")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8" s="6">
         <f>COUNTIF(Table6[[Least]:[2nd Least (is tied or to offset the tied mosts)]],"Avoiding")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2669,11 +2287,11 @@
     <row r="10" spans="1:3">
       <c r="B10" s="7">
         <f>SUM(B4:B9)</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C4:C9)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="6:10" ht="16.5" customHeight="1"/>
@@ -2733,15 +2351,15 @@
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
       <c r="Q1" s="10"/>
@@ -2860,20 +2478,14 @@
       <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>29</v>
-      </c>
+      <c r="B6" s="19"/>
       <c r="C6" s="17"/>
       <c r="D6" s="12"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="G6" s="19"/>
       <c r="H6" s="17"/>
-      <c r="I6" s="19" t="s">
-        <v>11</v>
-      </c>
+      <c r="I6" s="19"/>
       <c r="J6" s="17"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -2886,20 +2498,14 @@
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>30</v>
-      </c>
+      <c r="B7" s="20"/>
       <c r="C7" s="17"/>
       <c r="D7" s="12"/>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
-      <c r="G7" s="20" t="s">
-        <v>12</v>
-      </c>
+      <c r="G7" s="20"/>
       <c r="H7" s="17"/>
-      <c r="I7" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="I7" s="20"/>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -2912,20 +2518,14 @@
       <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>31</v>
-      </c>
+      <c r="B8" s="17"/>
       <c r="C8" s="18"/>
       <c r="D8" s="12"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="18" t="s">
-        <v>12</v>
-      </c>
+      <c r="G8" s="18"/>
       <c r="H8" s="17"/>
-      <c r="I8" s="18" t="s">
-        <v>14</v>
-      </c>
+      <c r="I8" s="18"/>
       <c r="J8" s="17"/>
       <c r="K8" s="18"/>
       <c r="L8" s="17"/>
@@ -2938,20 +2538,14 @@
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>32</v>
-      </c>
+      <c r="B9" s="20"/>
       <c r="C9" s="17"/>
       <c r="D9" s="12"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
-      <c r="G9" s="20" t="s">
-        <v>10</v>
-      </c>
+      <c r="G9" s="20"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="20" t="s">
-        <v>12</v>
-      </c>
+      <c r="I9" s="20"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -2964,22 +2558,14 @@
       <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>33</v>
-      </c>
+      <c r="B10" s="19"/>
       <c r="C10" s="17"/>
       <c r="D10" s="12"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>13</v>
-      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="19"/>
       <c r="J10" s="17"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
@@ -2992,20 +2578,14 @@
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>34</v>
-      </c>
+      <c r="B11" s="20"/>
       <c r="C11" s="17"/>
       <c r="D11" s="12"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
-      <c r="G11" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="G11" s="20"/>
       <c r="H11" s="17"/>
-      <c r="I11" s="20" t="s">
-        <v>12</v>
-      </c>
+      <c r="I11" s="20"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
@@ -3018,20 +2598,14 @@
       <c r="A12" s="9">
         <v>7</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>36</v>
-      </c>
+      <c r="B12" s="20"/>
       <c r="C12" s="17"/>
       <c r="D12" s="12"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
-      <c r="G12" s="20" t="s">
-        <v>13</v>
-      </c>
+      <c r="G12" s="20"/>
       <c r="H12" s="17"/>
-      <c r="I12" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="I12" s="20"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
@@ -3044,20 +2618,14 @@
       <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>37</v>
-      </c>
+      <c r="B13" s="19"/>
       <c r="C13" s="17"/>
       <c r="D13" s="12"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="19" t="s">
-        <v>10</v>
-      </c>
+      <c r="G13" s="19"/>
       <c r="H13" s="17"/>
-      <c r="I13" s="19" t="s">
-        <v>12</v>
-      </c>
+      <c r="I13" s="19"/>
       <c r="J13" s="17"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
@@ -3070,20 +2638,14 @@
       <c r="A14" s="9">
         <v>9</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>38</v>
-      </c>
+      <c r="B14" s="20"/>
       <c r="C14" s="17"/>
       <c r="D14" s="12"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
-      <c r="G14" s="20" t="s">
-        <v>10</v>
-      </c>
+      <c r="G14" s="20"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="20" t="s">
-        <v>13</v>
-      </c>
+      <c r="I14" s="20"/>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
@@ -3096,20 +2658,14 @@
       <c r="A15" s="16">
         <v>10</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>39</v>
-      </c>
+      <c r="B15" s="19"/>
       <c r="C15" s="17"/>
       <c r="D15" s="12"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="19" t="s">
-        <v>11</v>
-      </c>
+      <c r="G15" s="19"/>
       <c r="H15" s="17"/>
-      <c r="I15" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="I15" s="19"/>
       <c r="J15" s="17"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
@@ -3122,20 +2678,14 @@
       <c r="A16" s="9">
         <v>11</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>40</v>
-      </c>
+      <c r="B16" s="20"/>
       <c r="C16" s="17"/>
       <c r="D16" s="12"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
-      <c r="G16" s="20" t="s">
-        <v>10</v>
-      </c>
+      <c r="G16" s="20"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="20" t="s">
-        <v>13</v>
-      </c>
+      <c r="I16" s="20"/>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
@@ -3148,20 +2698,14 @@
       <c r="A17" s="9">
         <v>12</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>41</v>
-      </c>
+      <c r="B17" s="19"/>
       <c r="C17" s="17"/>
       <c r="D17" s="12"/>
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
-      <c r="G17" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="G17" s="19"/>
       <c r="H17" s="17"/>
-      <c r="I17" s="19" t="s">
-        <v>12</v>
-      </c>
+      <c r="I17" s="19"/>
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
@@ -3174,20 +2718,14 @@
       <c r="A18" s="16">
         <v>13</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>43</v>
-      </c>
+      <c r="B18" s="19"/>
       <c r="C18" s="17"/>
       <c r="D18" s="12"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
-      <c r="G18" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="G18" s="19"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="19" t="s">
-        <v>13</v>
-      </c>
+      <c r="I18" s="19"/>
       <c r="J18" s="17"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
@@ -3200,20 +2738,14 @@
       <c r="A19" s="16">
         <v>14</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>44</v>
-      </c>
+      <c r="B19" s="20"/>
       <c r="C19" s="17"/>
       <c r="D19" s="12"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="G19" s="20"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="20" t="s">
-        <v>13</v>
-      </c>
+      <c r="I19" s="20"/>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -3226,20 +2758,14 @@
       <c r="A20" s="9">
         <v>15</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>46</v>
-      </c>
+      <c r="B20" s="20"/>
       <c r="C20" s="17"/>
       <c r="D20" s="12"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
-      <c r="G20" s="20" t="s">
-        <v>14</v>
-      </c>
+      <c r="G20" s="20"/>
       <c r="H20" s="17"/>
-      <c r="I20" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="I20" s="20"/>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
@@ -3252,20 +2778,14 @@
       <c r="A21" s="9">
         <v>16</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>47</v>
-      </c>
+      <c r="B21" s="19"/>
       <c r="C21" s="17"/>
       <c r="D21" s="12"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
-      <c r="G21" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="G21" s="19"/>
       <c r="H21" s="17"/>
-      <c r="I21" s="19" t="s">
-        <v>11</v>
-      </c>
+      <c r="I21" s="19"/>
       <c r="J21" s="17"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
@@ -3328,157 +2848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{655B4E80-2DFF-449C-9D73-208146FFEACF}">
-  <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="4" width="9.140625"/>
-    <col min="5" max="5" width="7.140625" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="33.75">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="4">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4">
-        <f>COUNTIF(Table6[[Least]:[2nd Least (is tied or to offset the tied mosts)]],"Accommodating")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="4">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4">
-        <f>COUNTIF(Table6[[Most]:[2nd Most (If Tied or to offset tied Least)]],"Compromising")</f>
-        <v>3</v>
-      </c>
-      <c r="C7" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="6">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="B10" s="7">
-        <f>SUM(B4:B9)</f>
-        <v>17</v>
-      </c>
-      <c r="C10" s="7">
-        <f>SUM(C4:C9)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="6:10" ht="16.5" customHeight="1"/>
-    <row r="24" spans="6:10" ht="14.1" customHeight="1"/>
-    <row r="26" spans="6:10" ht="14.25">
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="8">
-        <v>43283</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:C8" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C8">
-      <sortCondition descending="1" ref="B5:B8"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a1725ccf-df03-4195-b247-89d3192cbd90" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="168aa859-81a9-4704-8be3-bd46f7ffa66e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CCDC69DD60195B4FBA5C00BA1CE18BF1" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ebfca71fd3d197a47a1627ef06e52290">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="168aa859-81a9-4704-8be3-bd46f7ffa66e" xmlns:ns3="a1725ccf-df03-4195-b247-89d3192cbd90" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff3c6f65af2c05bc9eb09f90b4e07643" ns2:_="" ns3:_="">
     <xsd:import namespace="168aa859-81a9-4704-8be3-bd46f7ffa66e"/>
@@ -3707,32 +3077,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9FB684E-294B-4C38-BB2A-F63421C664FA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a1725ccf-df03-4195-b247-89d3192cbd90"/>
-    <ds:schemaRef ds:uri="168aa859-81a9-4704-8be3-bd46f7ffa66e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78EEB585-AA94-4889-AC5C-52BF6E8EC3D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a1725ccf-df03-4195-b247-89d3192cbd90" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="168aa859-81a9-4704-8be3-bd46f7ffa66e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65F653E3-262C-42F9-BF6A-4A58B84C085A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3749,4 +3114,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78EEB585-AA94-4889-AC5C-52BF6E8EC3D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9FB684E-294B-4C38-BB2A-F63421C664FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1725ccf-df03-4195-b247-89d3192cbd90"/>
+    <ds:schemaRef ds:uri="168aa859-81a9-4704-8be3-bd46f7ffa66e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>